--- a/tencent_campus_jobs.xlsx
+++ b/tencent_campus_jobs.xlsx
@@ -5608,21 +5608,8 @@
           <t>不限/未提及</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>1、熟悉电脑绘图的创作流程和技巧，熟练掌握PS，以及其他常用2D设计软件，会3D辅助者优先；
-2、具有优秀的创造力和想象力，较强的文字理解力和表达能力，思维灵活，性格开朗，善于沟通与合作；
-3、较强的构图能力及立体构成设计能力，能适应多种绘画风格，热爱游戏，熟悉流行动漫及游戏文化，了解游戏中对不同风格的定位和差异。</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>1、负责项目前期风格探索的高概念氛围图；
-2、负责项目场景的氛围图，规划图，单体拆建设计；
-3、负责跟进并监督外包资源设计内容，把控外包资源最终品质；
-4、负责跟进与配合下游环节（3D场景）做好联调引擎里的效果。</t>
-        </is>
-      </c>
+      <c r="E130" s="3" t="inlineStr"/>
+      <c r="F130" s="3" t="inlineStr"/>
       <c r="G130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
